--- a/AtchisonRegime/Outputs/USA/USA500_Real_Estate/df_regSummary_USA500_Real_Estate.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500_Real_Estate/df_regSummary_USA500_Real_Estate.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>1.033442711355242</v>
+        <v>1.129899417120397</v>
       </c>
       <c r="H2" t="n">
-        <v>4.070343018551587</v>
+        <v>4.053303579919326</v>
       </c>
       <c r="I2" t="n">
         <v>-8.10424767618815</v>
@@ -545,22 +545,22 @@
         <v>9.6248306252491</v>
       </c>
       <c r="K2" t="n">
-        <v>34.31372549019608</v>
+        <v>34.95145631067961</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>11.66666666666667</v>
+        <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1210484640780234</v>
+        <v>0.1396401339150191</v>
       </c>
       <c r="O2" t="n">
         <v>0.007551522381175291</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2378260967038175</v>
+        <v>0.2936011062148047</v>
       </c>
     </row>
     <row r="3">
@@ -603,7 +603,7 @@
         <v>6.84469377692436</v>
       </c>
       <c r="K3" t="n">
-        <v>25.49019607843137</v>
+        <v>25.24271844660194</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>7.202297448723289</v>
       </c>
       <c r="K4" t="n">
-        <v>8.823529411764707</v>
+        <v>8.737864077669903</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -719,7 +719,7 @@
         <v>7.360199774148531</v>
       </c>
       <c r="K5" t="n">
-        <v>31.37254901960784</v>
+        <v>31.06796116504854</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
